--- a/data/trans_orig/P1803_2016_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1803_2016_2023-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22067</t>
+          <t>21164</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44305</t>
+          <t>44564</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>37239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45088</t>
+          <t>43804</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74542</t>
+          <t>73967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>384787</t>
+          <t>384528</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>407025</t>
+          <t>407928</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309095</t>
+          <t>309816</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>329748</t>
+          <t>329619</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>701605</t>
+          <t>702180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>731059</t>
+          <t>732343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>7645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23830</t>
+          <t>23505</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22186</t>
+          <t>22543</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>45869</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33367</t>
+          <t>35070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61217</t>
+          <t>62754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353397</t>
+          <t>353722</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368988</t>
+          <t>369582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327825</t>
+          <t>326404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>350087</t>
+          <t>349730</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>688283</t>
+          <t>686746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>716133</t>
+          <t>714430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35653</t>
+          <t>36330</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20160</t>
+          <t>19849</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25300</t>
+          <t>25726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48883</t>
+          <t>49174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>486261</t>
+          <t>485584</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>505854</t>
+          <t>506016</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145963</t>
+          <t>146274</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160040</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639153</t>
+          <t>638862</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662736</t>
+          <t>662310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>39063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66957</t>
+          <t>69405</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39026</t>
+          <t>39300</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67733</t>
+          <t>68638</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84495</t>
+          <t>83791</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126819</t>
+          <t>125069</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1082681</t>
+          <t>1080233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1111525</t>
+          <t>1110575</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>758143</t>
+          <t>757238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>786850</t>
+          <t>786576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1848695</t>
+          <t>1850445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1891019</t>
+          <t>1891723</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>13943</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33112</t>
+          <t>31157</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>21807</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43523</t>
+          <t>45028</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40408</t>
+          <t>41077</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68414</t>
+          <t>71074</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>587594</t>
+          <t>589549</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>606260</t>
+          <t>606763</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>694721</t>
+          <t>693216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>717478</t>
+          <t>716437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1290536</t>
+          <t>1287876</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1318542</t>
+          <t>1317873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19036</t>
+          <t>18172</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30365</t>
+          <t>30879</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56880</t>
+          <t>60561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39985</t>
+          <t>39430</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71096</t>
+          <t>72641</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268109</t>
+          <t>268973</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282035</t>
+          <t>282454</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1025145</t>
+          <t>1021464</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1051660</t>
+          <t>1051146</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1298074</t>
+          <t>1296529</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1329185</t>
+          <t>1329740</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130317</t>
+          <t>130802</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>181371</t>
+          <t>180451</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>167980</t>
+          <t>168837</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>226806</t>
+          <t>223084</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>314070</t>
+          <t>312544</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>390752</t>
+          <t>389216</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3204351</t>
+          <t>3205271</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3255405</t>
+          <t>3254920</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3304790</t>
+          <t>3308512</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3363616</t>
+          <t>3362759</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6526566</t>
+          <t>6528102</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6603248</t>
+          <t>6604774</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -3361,32 +3361,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>69295</t>
+          <t>69563</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54405</t>
+          <t>53401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88440</t>
+          <t>87048</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3396,32 +3396,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>76502</t>
+          <t>80368</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>66433</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89813</t>
+          <t>94736</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3431,32 +3431,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>145797</t>
+          <t>149931</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>124944</t>
+          <t>127998</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168542</t>
+          <t>171454</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -3474,32 +3474,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>435917</t>
+          <t>481055</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>416772</t>
+          <t>463570</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>450807</t>
+          <t>497217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3509,32 +3509,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>370965</t>
+          <t>408043</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>357654</t>
+          <t>393675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>385694</t>
+          <t>421978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3544,32 +3544,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>806882</t>
+          <t>889098</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>784137</t>
+          <t>867575</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>827735</t>
+          <t>911031</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -3587,17 +3587,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3622,17 +3622,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3704,32 +3704,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37306</t>
+          <t>37572</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27499</t>
+          <t>26830</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50297</t>
+          <t>50958</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59035</t>
+          <t>63873</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48446</t>
+          <t>52836</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71892</t>
+          <t>77798</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3774,32 +3774,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>96341</t>
+          <t>101445</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80983</t>
+          <t>83327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113734</t>
+          <t>120206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -3817,32 +3817,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>414907</t>
+          <t>445640</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401916</t>
+          <t>432254</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>424714</t>
+          <t>456382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3852,32 +3852,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>323545</t>
+          <t>359270</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>310688</t>
+          <t>345345</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>334134</t>
+          <t>370307</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3887,32 +3887,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>738452</t>
+          <t>804910</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>721059</t>
+          <t>786149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>753810</t>
+          <t>823028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -3930,17 +3930,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4000,17 +4000,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4047,32 +4047,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>286992</t>
+          <t>47990</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58595</t>
+          <t>35815</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>516397</t>
+          <t>64725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4082,32 +4082,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15401</t>
+          <t>16995</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21668</t>
+          <t>24425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4117,32 +4117,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>302393</t>
+          <t>64984</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76698</t>
+          <t>51372</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>584901</t>
+          <t>82334</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -4160,32 +4160,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>381272</t>
+          <t>423622</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151867</t>
+          <t>406887</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>609669</t>
+          <t>435797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4195,32 +4195,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>151510</t>
+          <t>170502</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145243</t>
+          <t>163072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156545</t>
+          <t>175770</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4230,32 +4230,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>532782</t>
+          <t>594125</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250274</t>
+          <t>576775</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>758477</t>
+          <t>607737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>92,21%</t>
         </is>
       </c>
     </row>
@@ -4273,17 +4273,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4308,17 +4308,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4390,32 +4390,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70644</t>
+          <t>76240</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56056</t>
+          <t>60042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89029</t>
+          <t>96934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4425,32 +4425,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>84094</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41485</t>
+          <t>72379</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112496</t>
+          <t>102744</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4460,32 +4460,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>154738</t>
+          <t>163135</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105103</t>
+          <t>140858</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>185839</t>
+          <t>188419</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -4503,32 +4503,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>964175</t>
+          <t>1055603</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>945790</t>
+          <t>1034909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>978763</t>
+          <t>1071801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4538,32 +4538,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>893434</t>
+          <t>773720</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>865032</t>
+          <t>757871</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>936043</t>
+          <t>788236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4573,32 +4573,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1857609</t>
+          <t>1829323</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1826508</t>
+          <t>1804039</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907244</t>
+          <t>1851600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4733,32 +4733,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>30971</t>
+          <t>33220</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20597</t>
+          <t>22889</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43912</t>
+          <t>48632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4768,32 +4768,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>63927</t>
+          <t>69702</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47677</t>
+          <t>57915</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>83908</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4803,32 +4803,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>94899</t>
+          <t>102921</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73971</t>
+          <t>85592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114443</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -4846,32 +4846,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>444075</t>
+          <t>534744</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>431134</t>
+          <t>519332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>454449</t>
+          <t>545075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4881,32 +4881,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>777408</t>
+          <t>761148</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>762335</t>
+          <t>746942</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>793658</t>
+          <t>772935</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4916,32 +4916,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1221482</t>
+          <t>1295893</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1201938</t>
+          <t>1275931</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1242410</t>
+          <t>1313222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -4959,17 +4959,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5029,17 +5029,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5076,32 +5076,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14385</t>
+          <t>12417</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32446</t>
+          <t>29184</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5111,32 +5111,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42203</t>
+          <t>47351</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31663</t>
+          <t>36131</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56753</t>
+          <t>64003</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5146,32 +5146,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>56588</t>
+          <t>59768</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42718</t>
+          <t>45391</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79465</t>
+          <t>80075</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -5189,32 +5189,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>226122</t>
+          <t>224811</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208061</t>
+          <t>208044</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236321</t>
+          <t>232871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5224,32 +5224,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>718489</t>
+          <t>796245</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>703939</t>
+          <t>779593</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>729029</t>
+          <t>807465</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5259,32 +5259,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>944612</t>
+          <t>1021056</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>921735</t>
+          <t>1000749</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>958482</t>
+          <t>1035433</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -5302,17 +5302,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5372,17 +5372,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>509593</t>
+          <t>277002</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>275062</t>
+          <t>245388</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1029749</t>
+          <t>315149</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5454,32 +5454,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>341163</t>
+          <t>365182</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>286374</t>
+          <t>336110</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>382581</t>
+          <t>395059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5489,32 +5489,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>850756</t>
+          <t>642184</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>611096</t>
+          <t>596520</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1650639</t>
+          <t>693071</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -5532,32 +5532,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2866467</t>
+          <t>3165474</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2346311</t>
+          <t>3127327</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3100998</t>
+          <t>3197088</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5567,32 +5567,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3235351</t>
+          <t>3268930</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3193933</t>
+          <t>3239053</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3290140</t>
+          <t>3298002</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5602,32 +5602,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6101818</t>
+          <t>6434404</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5301935</t>
+          <t>6383517</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6341478</t>
+          <t>6480068</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -5645,17 +5645,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5680,17 +5680,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3576514</t>
+          <t>3634112</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3576514</t>
+          <t>3634112</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3576514</t>
+          <t>3634112</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5715,17 +5715,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6952574</t>
+          <t>7076588</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6952574</t>
+          <t>7076588</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6952574</t>
+          <t>7076588</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
